--- a/TDD_examples/CASE_3_HTS_HVDC/conductor_diagnostic.xlsx
+++ b/TDD_examples/CASE_3_HTS_HVDC/conductor_diagnostic.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spatial_distribution" sheetId="1" r:id="R7e31dec72c054678"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time_evolution" sheetId="2" r:id="R77aaefb888d848d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spatial_distribution" sheetId="1" r:id="R542048680d3043dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time_evolution" sheetId="2" r:id="Rf8b0e9c846374be0"/>
   </x:sheets>
 </x:workbook>
 </file>
